--- a/resources/Part_3_Statistics/S18_L109/3.11.Population-variance-unknown-t-score-exercise.xlsx
+++ b/resources/Part_3_Statistics/S18_L109/3.11.Population-variance-unknown-t-score-exercise.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18229"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya\Desktop\Statistics Course\Filming\Final excel\Section 3 - Inferential\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\GitRepos\StatisticsBAandDS\DataScienceBootcamp\resources\Part_3_Statistics\S18_L109\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9084"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="Salaries" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Confidence intervals, t-score</t>
   </si>
@@ -61,6 +61,39 @@
   </si>
   <si>
     <t>Determine which statistic to use for inference</t>
+  </si>
+  <si>
+    <t>TASK 1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean: </t>
+  </si>
+  <si>
+    <t>Std Deviation:</t>
+  </si>
+  <si>
+    <t>Std Error:</t>
+  </si>
+  <si>
+    <t>Task 2:</t>
+  </si>
+  <si>
+    <t>Let's use T statistics for a small sample with unknown std deviation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 3: </t>
+  </si>
+  <si>
+    <t>9 samples -&gt; 8 degrees of freedom. 99% confidence</t>
+  </si>
+  <si>
+    <t>-&gt; 3,355</t>
+  </si>
+  <si>
+    <t>from:</t>
+  </si>
+  <si>
+    <t>up to:</t>
   </si>
 </sst>
 </file>
@@ -68,8 +101,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -155,10 +188,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -166,22 +199,27 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -494,26 +532,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:L21"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1"/>
+    <col min="4" max="4" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="9" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -521,7 +559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
@@ -529,7 +567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -537,7 +575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
@@ -545,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
@@ -553,46 +591,68 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="2:12" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>78000</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="D10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="10">
+        <f>SUM(B10:B18)/COUNT(B10:B18)</f>
+        <v>92533.333333333328</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="H10" s="7"/>
       <c r="I10" s="9"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-    </row>
-    <row r="11" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+      <c r="L10" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>90000</v>
       </c>
       <c r="C11" s="7"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
+      <c r="D11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="10">
+        <f>_xlfn.STDEV.S(B10:B18)</f>
+        <v>13931.887883556916</v>
+      </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
@@ -601,22 +661,37 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>75000</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
+      <c r="D12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="10">
+        <f>E11/SQRT(COUNT(B10:B18))</f>
+        <v>4643.9626278523056</v>
+      </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="G12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="15">
+        <f>E10-3.355*E11/SQRT(COUNT(B10:B18))</f>
+        <v>76952.838716888844</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="16">
+        <f>E10+3.355*E11/SQRT(COUNT(B10:B18))</f>
+        <v>108113.82794977781</v>
+      </c>
       <c r="K12" s="8"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>117000</v>
       </c>
@@ -631,7 +706,7 @@
       <c r="K13" s="10"/>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>105000</v>
       </c>
@@ -706,7 +781,7 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="2:12" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C19" s="8"/>
       <c r="D19" s="9"/>
       <c r="E19" s="7"/>
